--- a/data/Diessenhofen/investment_decision/Diessenhofen_MFH_from_2015_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_MFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>262.5571737453154</v>
+        <v>231.0495797214823</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>46009.44001874937</v>
       </c>
       <c r="F4" t="n">
-        <v>264.166586504826</v>
+        <v>229.1899479715638</v>
       </c>
       <c r="G4" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="H4" t="n">
-        <v>278.7900847991125</v>
+        <v>229.1899479715639</v>
       </c>
       <c r="I4" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="J4" t="n">
-        <v>281.1145497691217</v>
+        <v>229.1899479715639</v>
       </c>
       <c r="K4" t="n">
         <v>46009.44001874937</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>322.4952075306733</v>
+        <v>233.1931996455735</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>46009.44001874937</v>
       </c>
       <c r="F5" t="n">
-        <v>322.4952075306733</v>
+        <v>234.5880847302618</v>
       </c>
       <c r="G5" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="H5" t="n">
-        <v>347.0541884024183</v>
+        <v>234.7948190011706</v>
       </c>
       <c r="I5" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="J5" t="n">
-        <v>343.7205132448034</v>
+        <v>234.7943256107443</v>
       </c>
       <c r="K5" t="n">
         <v>46009.44001874937</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>322.4952075306733</v>
+        <v>233.1931996455735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>46009.44001874937</v>
       </c>
       <c r="F6" t="n">
-        <v>322.4952075306733</v>
+        <v>234.5880847302618</v>
       </c>
       <c r="G6" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="H6" t="n">
-        <v>347.0541884024183</v>
+        <v>234.7948190011706</v>
       </c>
       <c r="I6" t="n">
         <v>46009.44001874937</v>
       </c>
       <c r="J6" t="n">
-        <v>343.7205132448034</v>
+        <v>234.7943256107443</v>
       </c>
       <c r="K6" t="n">
         <v>46009.44001874937</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>69.01416002812405</v>
+        <v>146.557552247191</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02546470328235294</v>
+        <v>0.01742321803529412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02550726306123953</v>
+        <v>0.01742321803529412</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.0178978874234511</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.0178978874234511</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.01742321803529412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.01742321803529412</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.01789788742345111</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02680495082352941</v>
+        <v>0.01789788742345111</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02948544590588235</v>
+        <v>0.02144396065882353</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02948544590588235</v>
+        <v>0.0227842082</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03216594098823529</v>
+        <v>0.02301156954443713</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03216594098823529</v>
+        <v>0.02301156954443713</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03082569344705883</v>
+        <v>0.0227842082</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03216594098823529</v>
+        <v>0.02412445574117647</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03216594098823529</v>
+        <v>0.02412445574117647</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.3911586174473529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.39489764106243</v>
       </c>
       <c r="G19" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3274682981016383</v>
       </c>
       <c r="I19" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3309251624981275</v>
       </c>
       <c r="K19" t="n">
         <v>4.784683722</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>1.414870199829527</v>
+        <v>0.4097539268341165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F20" t="n">
-        <v>1.414870199829527</v>
+        <v>0.4220235890528688</v>
       </c>
       <c r="G20" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H20" t="n">
-        <v>1.414870199829527</v>
+        <v>0.3274682981016383</v>
       </c>
       <c r="I20" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J20" t="n">
-        <v>1.414870199829527</v>
+        <v>0.3309251624981275</v>
       </c>
       <c r="K20" t="n">
         <v>4.784683722</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>1.414870199829527</v>
+        <v>0.42240954334453</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F21" t="n">
-        <v>1.414870199829527</v>
+        <v>0.4220235890528688</v>
       </c>
       <c r="G21" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H21" t="n">
-        <v>1.414870199829527</v>
+        <v>0.3274682981016383</v>
       </c>
       <c r="I21" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J21" t="n">
-        <v>1.414870199829527</v>
+        <v>0.3309251624981275</v>
       </c>
       <c r="K21" t="n">
         <v>4.784683722</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2430711654834767</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.2460000854895982</v>
       </c>
       <c r="G29" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.2850105381765406</v>
       </c>
       <c r="I29" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2816117112500001</v>
       </c>
       <c r="K29" t="n">
         <v>4.784683722</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1.226095636948346</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.208414524260648</v>
       </c>
       <c r="G30" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.28360080659212</v>
       </c>
       <c r="I30" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.283563025220241</v>
       </c>
       <c r="K30" t="n">
         <v>4.784683722</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.27187742261906</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>4.784683722</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.267770129797285</v>
       </c>
       <c r="G31" t="n">
         <v>4.784683722</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.381347316898361</v>
       </c>
       <c r="I31" t="n">
         <v>4.784683722</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.366722458891923</v>
       </c>
       <c r="K31" t="n">
         <v>4.784683722</v>
@@ -2142,13 +2142,13 @@
         <v>14.11509099530798</v>
       </c>
       <c r="H46" t="n">
-        <v>14.11509099530798</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>14.11509099530798</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>14.11509099530798</v>
       </c>
       <c r="K46" t="n">
         <v>14.11509099530798</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.654140561629699</v>
+        <v>1.766599219013845</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F54" t="n">
-        <v>1.599108881492144</v>
+        <v>1.760208938302784</v>
       </c>
       <c r="G54" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H54" t="n">
-        <v>1.606028256680976</v>
+        <v>1.76291955992033</v>
       </c>
       <c r="I54" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J54" t="n">
-        <v>1.630062426050511</v>
+        <v>1.762424687922953</v>
       </c>
       <c r="K54" t="n">
         <v>16.13686314303654</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>2.373181028260834</v>
+        <v>2.624727124985617</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F55" t="n">
-        <v>2.325693470433484</v>
+        <v>2.575919581598043</v>
       </c>
       <c r="G55" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H55" t="n">
-        <v>2.286040271040481</v>
+        <v>2.591643324295385</v>
       </c>
       <c r="I55" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J55" t="n">
-        <v>2.336596972258254</v>
+        <v>2.532323107221017</v>
       </c>
       <c r="K55" t="n">
         <v>16.13686314303654</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>2.373181028260834</v>
+        <v>2.630257645642367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F56" t="n">
-        <v>2.325693470433485</v>
+        <v>2.575919581598043</v>
       </c>
       <c r="G56" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H56" t="n">
-        <v>2.286040271040481</v>
+        <v>2.591643324295385</v>
       </c>
       <c r="I56" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J56" t="n">
-        <v>2.336596972258254</v>
+        <v>2.53247456297022</v>
       </c>
       <c r="K56" t="n">
         <v>16.13686314303654</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>2.221001726768938</v>
+        <v>0.6041240265204139</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F64" t="n">
-        <v>2.268489284596287</v>
+        <v>0.6090498472284137</v>
       </c>
       <c r="G64" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H64" t="n">
-        <v>2.193022261152987</v>
+        <v>0.6063392256108684</v>
       </c>
       <c r="I64" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J64" t="n">
-        <v>2.158092162236534</v>
+        <v>0.6068340976082442</v>
       </c>
       <c r="K64" t="n">
         <v>16.13686314303654</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>2.221001726768938</v>
+        <v>0.7533983439806455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F65" t="n">
-        <v>2.268489284596287</v>
+        <v>0.7975902366306289</v>
       </c>
       <c r="G65" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H65" t="n">
-        <v>2.193022261152987</v>
+        <v>0.7820292971716272</v>
       </c>
       <c r="I65" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J65" t="n">
-        <v>2.158092162236534</v>
+        <v>0.8413491257010354</v>
       </c>
       <c r="K65" t="n">
         <v>16.13686314303654</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>2.221001726768938</v>
+        <v>0.7533983439806455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>16.13686314303654</v>
       </c>
       <c r="F66" t="n">
-        <v>2.268489284596287</v>
+        <v>0.7975902366306289</v>
       </c>
       <c r="G66" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="H66" t="n">
-        <v>2.193022261152987</v>
+        <v>0.7820292971716272</v>
       </c>
       <c r="I66" t="n">
         <v>16.13686314303654</v>
       </c>
       <c r="J66" t="n">
-        <v>2.158092162236534</v>
+        <v>0.8413491257010354</v>
       </c>
       <c r="K66" t="n">
         <v>16.13686314303654</v>
